--- a/reports/telegram/aegis_usa_2026-09-02.xlsx
+++ b/reports/telegram/aegis_usa_2026-09-02.xlsx
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M98" s="4" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M103" s="4" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M105" s="4" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M109" s="4" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M110" s="4" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M125" s="4" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M133" s="4" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M143" s="4" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M145" s="4" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M146" s="4" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M147" s="4" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M159" s="4" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M165" s="4" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M167" s="4" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M168" s="4" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M169" s="4" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M171" s="4" t="inlineStr">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M172" s="4" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M173" s="4" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M174" s="4" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M175" s="4" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M181" s="4" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M183" s="4" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M185" s="4" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M188" s="4" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M191" s="4" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M193" s="4" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M195" s="4" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="L197" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M198" s="4" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="L199" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M199" s="4" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M200" s="4" t="inlineStr">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M201" s="4" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M202" s="4" t="inlineStr">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M203" s="4" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M204" s="4" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M206" s="4" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M207" s="4" t="inlineStr">
@@ -14967,7 +14967,7 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M208" s="4" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M209" s="4" t="inlineStr">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M210" s="4" t="inlineStr">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M211" s="4" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M212" s="4" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="L213" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M213" s="4" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M214" s="4" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M215" s="4" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -15476,7 +15476,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M216" s="4" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="L217" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M217" s="4" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M218" s="4" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="L219" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M219" s="4" t="inlineStr">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M220" s="4" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="L221" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M221" s="4" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M222" s="4" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="L223" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M223" s="4" t="inlineStr">
@@ -15911,7 +15911,7 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M224" s="4" t="inlineStr">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -16007,7 +16007,7 @@
       </c>
       <c r="L225" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M225" s="4" t="inlineStr">
@@ -16029,7 +16029,7 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M226" s="4" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="L227" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M227" s="4" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M228" s="4" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="L229" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M229" s="4" t="inlineStr">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
@@ -16302,7 +16302,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M230" s="4" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="L231" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M231" s="4" t="inlineStr">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M232" s="4" t="inlineStr">
@@ -16442,7 +16442,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M233" s="4" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M234" s="4" t="inlineStr">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="L235" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M235" s="4" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M236" s="4" t="inlineStr">
@@ -16678,7 +16678,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="L237" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M237" s="4" t="inlineStr">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M238" s="4" t="inlineStr">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L239" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M239" s="4" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M240" s="4" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="L241" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M241" s="4" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M242" s="4" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="L243" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M243" s="4" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -17128,7 +17128,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M244" s="4" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="L245" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M245" s="4" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M246" s="4" t="inlineStr">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -17305,7 +17305,7 @@
       </c>
       <c r="L247" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M247" s="4" t="inlineStr">
@@ -17327,7 +17327,7 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -17364,7 +17364,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M248" s="4" t="inlineStr">
@@ -17386,7 +17386,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -17423,7 +17423,7 @@
       </c>
       <c r="L249" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M249" s="4" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -17482,7 +17482,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M250" s="4" t="inlineStr">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -17541,7 +17541,7 @@
       </c>
       <c r="L251" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M251" s="4" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M252" s="4" t="inlineStr">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="L253" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M253" s="4" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M254" s="4" t="inlineStr">
@@ -17740,7 +17740,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="L255" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M255" s="4" t="inlineStr">
@@ -17799,7 +17799,7 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -17836,7 +17836,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M256" s="4" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="L257" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M257" s="4" t="inlineStr">
@@ -17917,7 +17917,7 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -17954,7 +17954,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M258" s="4" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -18013,7 +18013,7 @@
       </c>
       <c r="L259" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M259" s="4" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M260" s="4" t="inlineStr">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="L261" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M261" s="4" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -18190,7 +18190,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M262" s="4" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -18249,7 +18249,7 @@
       </c>
       <c r="L263" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M263" s="4" t="inlineStr">
@@ -18271,7 +18271,7 @@
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M264" s="4" t="inlineStr">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="L265" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M265" s="4" t="inlineStr">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M266" s="4" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -18485,7 +18485,7 @@
       </c>
       <c r="L267" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M267" s="4" t="inlineStr">
@@ -18507,7 +18507,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M268" s="4" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -18603,7 +18603,7 @@
       </c>
       <c r="L269" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M269" s="4" t="inlineStr">
@@ -18625,7 +18625,7 @@
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M270" s="4" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -18721,7 +18721,7 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M272" s="4" t="inlineStr">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="L273" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M273" s="4" t="inlineStr">
@@ -18861,7 +18861,7 @@
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M274" s="4" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="L275" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M275" s="4" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M276" s="4" t="inlineStr">
@@ -19038,7 +19038,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -19075,7 +19075,7 @@
       </c>
       <c r="L277" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M277" s="4" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M278" s="4" t="inlineStr">
@@ -19156,7 +19156,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -19193,7 +19193,7 @@
       </c>
       <c r="L279" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M279" s="4" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M280" s="4" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="L281" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M281" s="4" t="inlineStr">
@@ -19333,7 +19333,7 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M282" s="4" t="inlineStr">
@@ -19392,7 +19392,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="L283" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M283" s="4" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M284" s="4" t="inlineStr">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="L285" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M285" s="4" t="inlineStr">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -19606,7 +19606,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M286" s="4" t="inlineStr">
@@ -19628,7 +19628,7 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="L287" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M287" s="4" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M288" s="4" t="inlineStr">
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="L289" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M289" s="4" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M290" s="4" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="L291" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M291" s="4" t="inlineStr">
@@ -19923,7 +19923,7 @@
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M292" s="4" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="L293" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M293" s="4" t="inlineStr">
@@ -20041,7 +20041,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -20078,7 +20078,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M294" s="4" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -20137,7 +20137,7 @@
       </c>
       <c r="L295" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M295" s="4" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M296" s="4" t="inlineStr">
@@ -20218,7 +20218,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="L297" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M297" s="4" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M298" s="4" t="inlineStr">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="L299" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M299" s="4" t="inlineStr">
@@ -20395,7 +20395,7 @@
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -20432,7 +20432,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M300" s="4" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="L301" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M301" s="4" t="inlineStr">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M302" s="4" t="inlineStr">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="L303" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M303" s="4" t="inlineStr">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M304" s="4" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="L305" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M305" s="4" t="inlineStr">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -20786,7 +20786,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M306" s="4" t="inlineStr">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="L307" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M307" s="4" t="inlineStr">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -20904,7 +20904,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M308" s="4" t="inlineStr">
@@ -20926,7 +20926,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="L309" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M309" s="4" t="inlineStr">
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M310" s="4" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -21081,7 +21081,7 @@
       </c>
       <c r="L311" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M311" s="4" t="inlineStr">
@@ -21103,7 +21103,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M312" s="4" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -21199,7 +21199,7 @@
       </c>
       <c r="L313" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M313" s="4" t="inlineStr">
@@ -21221,7 +21221,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -21258,7 +21258,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M314" s="4" t="inlineStr">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="L315" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M315" s="4" t="inlineStr">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -21376,7 +21376,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M316" s="4" t="inlineStr">
@@ -21398,7 +21398,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="L317" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M317" s="4" t="inlineStr">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M318" s="4" t="inlineStr">
@@ -21516,7 +21516,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -21553,7 +21553,7 @@
       </c>
       <c r="L319" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M319" s="4" t="inlineStr">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -21612,7 +21612,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M320" s="4" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -21671,7 +21671,7 @@
       </c>
       <c r="L321" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M321" s="4" t="inlineStr">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M322" s="4" t="inlineStr">
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="L323" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M323" s="4" t="inlineStr">
@@ -21811,7 +21811,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -21848,7 +21848,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M324" s="4" t="inlineStr">
@@ -21870,7 +21870,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="L325" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M325" s="4" t="inlineStr">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -21966,7 +21966,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M326" s="4" t="inlineStr">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="L327" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M327" s="4" t="inlineStr">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M328" s="4" t="inlineStr">
@@ -22106,7 +22106,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="L329" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M329" s="4" t="inlineStr">
@@ -22165,7 +22165,7 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -22202,7 +22202,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M330" s="4" t="inlineStr">
@@ -22224,7 +22224,7 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="L331" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M331" s="4" t="inlineStr">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
@@ -22320,7 +22320,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M332" s="4" t="inlineStr">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -22379,7 +22379,7 @@
       </c>
       <c r="L333" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M333" s="4" t="inlineStr">
@@ -22401,7 +22401,7 @@
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -22438,7 +22438,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M334" s="4" t="inlineStr">
@@ -22460,7 +22460,7 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="L335" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M335" s="4" t="inlineStr">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M336" s="4" t="inlineStr">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -22615,7 +22615,7 @@
       </c>
       <c r="L337" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M337" s="4" t="inlineStr">
@@ -22637,7 +22637,7 @@
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M338" s="4" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -22733,7 +22733,7 @@
       </c>
       <c r="L339" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M339" s="4" t="inlineStr">
@@ -22755,7 +22755,7 @@
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M340" s="4" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="L341" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M341" s="4" t="inlineStr">
@@ -22873,7 +22873,7 @@
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
@@ -22910,7 +22910,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M342" s="4" t="inlineStr">
@@ -22932,7 +22932,7 @@
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -22969,7 +22969,7 @@
       </c>
       <c r="L343" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M343" s="4" t="inlineStr">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M344" s="4" t="inlineStr">
@@ -23050,7 +23050,7 @@
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="L345" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M345" s="4" t="inlineStr">
@@ -23109,7 +23109,7 @@
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M346" s="4" t="inlineStr">
@@ -23168,7 +23168,7 @@
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="L347" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M347" s="4" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D348" s="4" t="inlineStr">
@@ -23264,7 +23264,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M348" s="4" t="inlineStr">
@@ -23286,7 +23286,7 @@
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -23323,7 +23323,7 @@
       </c>
       <c r="L349" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M349" s="4" t="inlineStr">
@@ -23345,7 +23345,7 @@
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D350" s="4" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M350" s="4" t="inlineStr">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="L351" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M351" s="4" t="inlineStr">
@@ -23463,7 +23463,7 @@
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
@@ -23500,7 +23500,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M352" s="4" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="L353" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M353" s="4" t="inlineStr">
@@ -23581,7 +23581,7 @@
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M354" s="4" t="inlineStr">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -23677,7 +23677,7 @@
       </c>
       <c r="L355" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M355" s="4" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D356" s="4" t="inlineStr">
@@ -23736,7 +23736,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M356" s="4" t="inlineStr">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="L357" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M357" s="4" t="inlineStr">
@@ -23817,7 +23817,7 @@
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D358" s="4" t="inlineStr">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M358" s="4" t="inlineStr">
@@ -23876,7 +23876,7 @@
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -23913,7 +23913,7 @@
       </c>
       <c r="L359" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M359" s="4" t="inlineStr">
@@ -23935,7 +23935,7 @@
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M360" s="4" t="inlineStr">
@@ -23994,7 +23994,7 @@
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -24031,7 +24031,7 @@
       </c>
       <c r="L361" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M361" s="4" t="inlineStr">
@@ -24053,7 +24053,7 @@
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
@@ -24090,7 +24090,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M362" s="4" t="inlineStr">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="L363" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M363" s="4" t="inlineStr">
@@ -24171,7 +24171,7 @@
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M364" s="4" t="inlineStr">
@@ -24230,7 +24230,7 @@
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -24267,7 +24267,7 @@
       </c>
       <c r="L365" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M365" s="4" t="inlineStr">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M366" s="4" t="inlineStr">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -24385,7 +24385,7 @@
       </c>
       <c r="L367" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M367" s="4" t="inlineStr">
@@ -24407,7 +24407,7 @@
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M368" s="4" t="inlineStr">
@@ -24466,7 +24466,7 @@
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
@@ -24503,7 +24503,7 @@
       </c>
       <c r="L369" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M369" s="4" t="inlineStr">
@@ -24525,7 +24525,7 @@
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
@@ -24562,7 +24562,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M370" s="4" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
@@ -24621,7 +24621,7 @@
       </c>
       <c r="L371" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M371" s="4" t="inlineStr">
@@ -24643,7 +24643,7 @@
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D372" s="4" t="inlineStr">
@@ -24680,7 +24680,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M372" s="4" t="inlineStr">
@@ -24702,7 +24702,7 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="L373" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M373" s="4" t="inlineStr">
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D374" s="4" t="inlineStr">
@@ -24798,7 +24798,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M374" s="4" t="inlineStr">
@@ -24820,7 +24820,7 @@
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
@@ -24857,7 +24857,7 @@
       </c>
       <c r="L375" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M375" s="4" t="inlineStr">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D376" s="4" t="inlineStr">
@@ -24916,7 +24916,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M376" s="4" t="inlineStr">
@@ -24938,7 +24938,7 @@
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
@@ -24975,7 +24975,7 @@
       </c>
       <c r="L377" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M377" s="4" t="inlineStr">
@@ -24997,7 +24997,7 @@
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
@@ -25034,7 +25034,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M378" s="4" t="inlineStr">
@@ -25056,7 +25056,7 @@
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="L379" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M379" s="4" t="inlineStr">
@@ -25115,7 +25115,7 @@
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D380" s="4" t="inlineStr">
@@ -25152,7 +25152,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M380" s="4" t="inlineStr">
@@ -25174,7 +25174,7 @@
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
@@ -25211,7 +25211,7 @@
       </c>
       <c r="L381" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M381" s="4" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M382" s="4" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="L383" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M383" s="4" t="inlineStr">
@@ -25351,7 +25351,7 @@
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D384" s="4" t="inlineStr">
@@ -25388,7 +25388,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M384" s="4" t="inlineStr">
@@ -25410,7 +25410,7 @@
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
@@ -25447,7 +25447,7 @@
       </c>
       <c r="L385" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M385" s="4" t="inlineStr">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M386" s="4" t="inlineStr">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="L387" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M387" s="4" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M388" s="4" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="L389" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M389" s="4" t="inlineStr">
@@ -25705,7 +25705,7 @@
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D390" s="4" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M390" s="4" t="inlineStr">
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="L391" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M391" s="4" t="inlineStr">
@@ -25823,7 +25823,7 @@
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D392" s="4" t="inlineStr">
@@ -25860,7 +25860,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M392" s="4" t="inlineStr">
@@ -25882,7 +25882,7 @@
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
@@ -25919,7 +25919,7 @@
       </c>
       <c r="L393" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M393" s="4" t="inlineStr">
@@ -25941,7 +25941,7 @@
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D394" s="4" t="inlineStr">
@@ -25978,7 +25978,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M394" s="4" t="inlineStr">
@@ -26000,7 +26000,7 @@
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -26037,7 +26037,7 @@
       </c>
       <c r="L395" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M395" s="4" t="inlineStr">
@@ -26059,7 +26059,7 @@
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D396" s="4" t="inlineStr">
@@ -26096,7 +26096,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M396" s="4" t="inlineStr">
@@ -26118,7 +26118,7 @@
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -26155,7 +26155,7 @@
       </c>
       <c r="L397" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M397" s="4" t="inlineStr">
@@ -26177,7 +26177,7 @@
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr">
@@ -26214,7 +26214,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M398" s="4" t="inlineStr">
@@ -26236,7 +26236,7 @@
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -26273,7 +26273,7 @@
       </c>
       <c r="L399" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M399" s="4" t="inlineStr">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D400" s="4" t="inlineStr">
@@ -26332,7 +26332,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M400" s="4" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -26391,7 +26391,7 @@
       </c>
       <c r="L401" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M401" s="4" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D402" s="4" t="inlineStr">
@@ -26450,7 +26450,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M402" s="4" t="inlineStr">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
@@ -26509,7 +26509,7 @@
       </c>
       <c r="L403" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M403" s="4" t="inlineStr">
@@ -26531,7 +26531,7 @@
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D404" s="4" t="inlineStr">
@@ -26568,7 +26568,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M404" s="4" t="inlineStr">
@@ -26590,7 +26590,7 @@
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
@@ -26627,7 +26627,7 @@
       </c>
       <c r="L405" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M405" s="4" t="inlineStr">
@@ -26649,7 +26649,7 @@
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D406" s="4" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M406" s="4" t="inlineStr">
@@ -26708,7 +26708,7 @@
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D407" s="4" t="inlineStr">
@@ -26745,7 +26745,7 @@
       </c>
       <c r="L407" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M407" s="4" t="inlineStr">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D408" s="4" t="inlineStr">
@@ -26804,7 +26804,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M408" s="4" t="inlineStr">
@@ -26826,7 +26826,7 @@
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D409" s="4" t="inlineStr">
@@ -26863,7 +26863,7 @@
       </c>
       <c r="L409" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M409" s="4" t="inlineStr">
@@ -26885,7 +26885,7 @@
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D410" s="4" t="inlineStr">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M410" s="4" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="L411" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M411" s="4" t="inlineStr">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D412" s="4" t="inlineStr">
@@ -27040,7 +27040,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M412" s="4" t="inlineStr">
@@ -27062,7 +27062,7 @@
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
@@ -27099,7 +27099,7 @@
       </c>
       <c r="L413" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M413" s="4" t="inlineStr">
@@ -27121,7 +27121,7 @@
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D414" s="4" t="inlineStr">
@@ -27158,7 +27158,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M414" s="4" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
@@ -27217,7 +27217,7 @@
       </c>
       <c r="L415" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M415" s="4" t="inlineStr">
@@ -27239,7 +27239,7 @@
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D416" s="4" t="inlineStr">
@@ -27276,7 +27276,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M416" s="4" t="inlineStr">
@@ -27298,7 +27298,7 @@
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr">
@@ -27335,7 +27335,7 @@
       </c>
       <c r="L417" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M417" s="4" t="inlineStr">
@@ -27357,7 +27357,7 @@
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D418" s="4" t="inlineStr">
@@ -27394,7 +27394,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M418" s="4" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
@@ -27453,7 +27453,7 @@
       </c>
       <c r="L419" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M419" s="4" t="inlineStr">
@@ -27475,7 +27475,7 @@
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D420" s="4" t="inlineStr">
@@ -27512,7 +27512,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M420" s="4" t="inlineStr">
@@ -27534,7 +27534,7 @@
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
@@ -27571,7 +27571,7 @@
       </c>
       <c r="L421" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M421" s="4" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D422" s="4" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M422" s="4" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="L423" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M423" s="4" t="inlineStr">
@@ -27711,7 +27711,7 @@
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D424" s="4" t="inlineStr">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M424" s="4" t="inlineStr">
@@ -27770,7 +27770,7 @@
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
@@ -27807,7 +27807,7 @@
       </c>
       <c r="L425" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M425" s="4" t="inlineStr">
@@ -27829,7 +27829,7 @@
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D426" s="4" t="inlineStr">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M426" s="4" t="inlineStr">
@@ -27888,7 +27888,7 @@
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
@@ -27925,7 +27925,7 @@
       </c>
       <c r="L427" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M427" s="4" t="inlineStr">
@@ -27947,7 +27947,7 @@
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D428" s="4" t="inlineStr">
@@ -27984,7 +27984,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M428" s="4" t="inlineStr">
@@ -28006,7 +28006,7 @@
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
@@ -28043,7 +28043,7 @@
       </c>
       <c r="L429" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M429" s="4" t="inlineStr">
@@ -28065,7 +28065,7 @@
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D430" s="4" t="inlineStr">
@@ -28102,7 +28102,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M430" s="4" t="inlineStr">
@@ -28124,7 +28124,7 @@
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="L431" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M431" s="4" t="inlineStr">
@@ -28183,7 +28183,7 @@
       </c>
       <c r="C432" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D432" s="4" t="inlineStr">
@@ -28220,7 +28220,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M432" s="4" t="inlineStr">
@@ -28242,7 +28242,7 @@
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
@@ -28279,7 +28279,7 @@
       </c>
       <c r="L433" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M433" s="4" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D434" s="4" t="inlineStr">
@@ -28338,7 +28338,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M434" s="4" t="inlineStr">
@@ -28360,7 +28360,7 @@
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
@@ -28397,7 +28397,7 @@
       </c>
       <c r="L435" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M435" s="4" t="inlineStr">
@@ -28419,7 +28419,7 @@
       </c>
       <c r="C436" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D436" s="4" t="inlineStr">
@@ -28456,7 +28456,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M436" s="4" t="inlineStr">
@@ -28478,7 +28478,7 @@
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
@@ -28515,7 +28515,7 @@
       </c>
       <c r="L437" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M437" s="4" t="inlineStr">
@@ -28537,7 +28537,7 @@
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D438" s="4" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M438" s="4" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
@@ -28633,7 +28633,7 @@
       </c>
       <c r="L439" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M439" s="4" t="inlineStr">
@@ -28655,7 +28655,7 @@
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D440" s="4" t="inlineStr">
@@ -28692,7 +28692,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M440" s="4" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="C441" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D441" s="4" t="inlineStr">
@@ -28751,7 +28751,7 @@
       </c>
       <c r="L441" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M441" s="4" t="inlineStr">
@@ -28773,7 +28773,7 @@
       </c>
       <c r="C442" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D442" s="4" t="inlineStr">
@@ -28810,7 +28810,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M442" s="4" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
@@ -28869,7 +28869,7 @@
       </c>
       <c r="L443" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M443" s="4" t="inlineStr">
@@ -28891,7 +28891,7 @@
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D444" s="4" t="inlineStr">
@@ -28928,7 +28928,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M444" s="4" t="inlineStr">
@@ -28950,7 +28950,7 @@
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D445" s="4" t="inlineStr">
@@ -28987,7 +28987,7 @@
       </c>
       <c r="L445" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M445" s="4" t="inlineStr">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="C446" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D446" s="4" t="inlineStr">
@@ -29046,7 +29046,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M446" s="4" t="inlineStr">
@@ -29068,7 +29068,7 @@
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D447" s="4" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="L447" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M447" s="4" t="inlineStr">
@@ -29127,7 +29127,7 @@
       </c>
       <c r="C448" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D448" s="4" t="inlineStr">
@@ -29164,7 +29164,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M448" s="4" t="inlineStr">
@@ -29186,7 +29186,7 @@
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D449" s="4" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="L449" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M449" s="4" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="C450" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D450" s="4" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M450" s="4" t="inlineStr">
@@ -29304,7 +29304,7 @@
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D451" s="4" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="L451" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M451" s="4" t="inlineStr">
@@ -29363,7 +29363,7 @@
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D452" s="4" t="inlineStr">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M452" s="4" t="inlineStr">
@@ -29422,7 +29422,7 @@
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D453" s="4" t="inlineStr">
@@ -29459,7 +29459,7 @@
       </c>
       <c r="L453" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M453" s="4" t="inlineStr">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="C454" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D454" s="4" t="inlineStr">
@@ -29518,7 +29518,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M454" s="4" t="inlineStr">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C455" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D455" s="4" t="inlineStr">
@@ -29577,7 +29577,7 @@
       </c>
       <c r="L455" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M455" s="4" t="inlineStr">
@@ -29599,7 +29599,7 @@
       </c>
       <c r="C456" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D456" s="4" t="inlineStr">
@@ -29636,7 +29636,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M456" s="4" t="inlineStr">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C457" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D457" s="4" t="inlineStr">
@@ -29695,7 +29695,7 @@
       </c>
       <c r="L457" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M457" s="4" t="inlineStr">
@@ -29717,7 +29717,7 @@
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D458" s="4" t="inlineStr">
@@ -29754,7 +29754,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M458" s="4" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D459" s="4" t="inlineStr">
@@ -29813,7 +29813,7 @@
       </c>
       <c r="L459" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M459" s="4" t="inlineStr">
@@ -29835,7 +29835,7 @@
       </c>
       <c r="C460" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D460" s="4" t="inlineStr">
@@ -29872,7 +29872,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M460" s="4" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D461" s="4" t="inlineStr">
@@ -29931,7 +29931,7 @@
       </c>
       <c r="L461" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M461" s="4" t="inlineStr">
@@ -29953,7 +29953,7 @@
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D462" s="4" t="inlineStr">
@@ -29990,7 +29990,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M462" s="4" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="C463" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D463" s="4" t="inlineStr">
@@ -30049,7 +30049,7 @@
       </c>
       <c r="L463" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M463" s="4" t="inlineStr">
@@ -30071,7 +30071,7 @@
       </c>
       <c r="C464" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D464" s="4" t="inlineStr">
@@ -30108,7 +30108,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M464" s="4" t="inlineStr">
@@ -30130,7 +30130,7 @@
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">
@@ -30167,7 +30167,7 @@
       </c>
       <c r="L465" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M465" s="4" t="inlineStr">
@@ -30189,7 +30189,7 @@
       </c>
       <c r="C466" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D466" s="4" t="inlineStr">
@@ -30226,7 +30226,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M466" s="4" t="inlineStr">
@@ -30248,7 +30248,7 @@
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
@@ -30285,7 +30285,7 @@
       </c>
       <c r="L467" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M467" s="4" t="inlineStr">
@@ -30307,7 +30307,7 @@
       </c>
       <c r="C468" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D468" s="4" t="inlineStr">
@@ -30344,7 +30344,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GOOGL (+57.4pp)</t>
+          <t>Rotation swap · +57.4 pp</t>
         </is>
       </c>
       <c r="M468" s="4" t="inlineStr">
@@ -30366,7 +30366,7 @@
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D469" s="4" t="inlineStr">
@@ -30403,7 +30403,7 @@
       </c>
       <c r="L469" s="4" t="inlineStr">
         <is>
-          <t>Rotation → UBER (+60.6pp)</t>
+          <t>Rotation swap · +60.6 pp</t>
         </is>
       </c>
       <c r="M469" s="4" t="inlineStr">
@@ -30425,7 +30425,7 @@
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D470" s="4" t="inlineStr">
@@ -30462,7 +30462,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>Rotation → UBER (+60.5pp)</t>
+          <t>Rotation swap · +60.5 pp</t>
         </is>
       </c>
       <c r="M470" s="4" t="inlineStr">
@@ -30484,7 +30484,7 @@
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D471" s="4" t="inlineStr">
@@ -30521,7 +30521,7 @@
       </c>
       <c r="L471" s="4" t="inlineStr">
         <is>
-          <t>Rotation → BMY (+59.4pp)</t>
+          <t>Rotation swap · +59.4 pp</t>
         </is>
       </c>
       <c r="M471" s="4" t="inlineStr">
@@ -30543,7 +30543,7 @@
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D472" s="4" t="inlineStr">
@@ -30580,7 +30580,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>→ BMY · +9.9pp alpha</t>
+          <t>Outperformance exit · +9.9 pp</t>
         </is>
       </c>
       <c r="M472" s="4" t="inlineStr">
@@ -30602,7 +30602,7 @@
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D473" s="4" t="inlineStr">
@@ -30639,7 +30639,7 @@
       </c>
       <c r="L473" s="4" t="inlineStr">
         <is>
-          <t>→ BMY · +63.2pp alpha</t>
+          <t>Outperformance exit · +63.2 pp</t>
         </is>
       </c>
       <c r="M473" s="4" t="inlineStr">
@@ -30661,7 +30661,7 @@
       </c>
       <c r="C474" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D474" s="4" t="inlineStr">
@@ -30698,7 +30698,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>→ BMY · +9.9pp alpha</t>
+          <t>Outperformance exit · +9.9 pp</t>
         </is>
       </c>
       <c r="M474" s="4" t="inlineStr">
@@ -30720,7 +30720,7 @@
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D475" s="4" t="inlineStr">
@@ -30757,7 +30757,7 @@
       </c>
       <c r="L475" s="4" t="inlineStr">
         <is>
-          <t>→ BMY · +9.8pp alpha</t>
+          <t>Outperformance exit · +9.8 pp</t>
         </is>
       </c>
       <c r="M475" s="4" t="inlineStr">
@@ -30779,7 +30779,7 @@
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D476" s="4" t="inlineStr">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +61.4pp alpha</t>
+          <t>Outperformance exit · +61.4 pp</t>
         </is>
       </c>
       <c r="M476" s="4" t="inlineStr">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="L477" s="4" t="inlineStr">
         <is>
-          <t>→ ADSK · +57.6pp alpha</t>
+          <t>Outperformance exit · +57.6 pp</t>
         </is>
       </c>
       <c r="M477" s="4" t="inlineStr">
@@ -30897,7 +30897,7 @@
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D478" s="4" t="inlineStr">
@@ -30934,7 +30934,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +5.7pp alpha</t>
+          <t>Outperformance exit · +5.7 pp</t>
         </is>
       </c>
       <c r="M478" s="4" t="inlineStr">
@@ -30956,7 +30956,7 @@
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
@@ -30993,7 +30993,7 @@
       </c>
       <c r="L479" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +5.4pp alpha</t>
+          <t>Outperformance exit · +5.4 pp</t>
         </is>
       </c>
       <c r="M479" s="4" t="inlineStr">
@@ -31015,7 +31015,7 @@
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D480" s="4" t="inlineStr">
@@ -31052,7 +31052,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>→ ADSK · +59.4pp alpha</t>
+          <t>Outperformance exit · +59.4 pp</t>
         </is>
       </c>
       <c r="M480" s="4" t="inlineStr">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D481" s="4" t="inlineStr">
@@ -31111,7 +31111,7 @@
       </c>
       <c r="L481" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +62.3pp alpha</t>
+          <t>Outperformance exit · +62.3 pp</t>
         </is>
       </c>
       <c r="M481" s="4" t="inlineStr">
@@ -31133,7 +31133,7 @@
       </c>
       <c r="C482" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D482" s="4" t="inlineStr">
@@ -31170,7 +31170,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +5.1pp alpha</t>
+          <t>Outperformance exit · +5.1 pp</t>
         </is>
       </c>
       <c r="M482" s="4" t="inlineStr">
@@ -31192,7 +31192,7 @@
       </c>
       <c r="C483" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D483" s="4" t="inlineStr">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="L483" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +5.2pp alpha</t>
+          <t>Outperformance exit · +5.2 pp</t>
         </is>
       </c>
       <c r="M483" s="4" t="inlineStr">
@@ -31251,7 +31251,7 @@
       </c>
       <c r="C484" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D484" s="4" t="inlineStr">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>→ ADSK · +58.4pp alpha</t>
+          <t>Outperformance exit · +58.4 pp</t>
         </is>
       </c>
       <c r="M484" s="4" t="inlineStr">
@@ -31310,7 +31310,7 @@
       </c>
       <c r="C485" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D485" s="4" t="inlineStr">
@@ -31347,7 +31347,7 @@
       </c>
       <c r="L485" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +5.7pp alpha</t>
+          <t>Outperformance exit · +5.7 pp</t>
         </is>
       </c>
       <c r="M485" s="4" t="inlineStr">
@@ -31369,7 +31369,7 @@
       </c>
       <c r="C486" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D486" s="4" t="inlineStr">
@@ -31406,7 +31406,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORPHAN_AUTO_CLOSE · CANONICAL_REPAIR v2 </t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M486" s="4" t="inlineStr">
@@ -31428,7 +31428,7 @@
       </c>
       <c r="C487" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D487" s="4" t="inlineStr">
@@ -31465,7 +31465,7 @@
       </c>
       <c r="L487" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +14.9pp alpha</t>
+          <t>Outperformance exit · +14.9 pp</t>
         </is>
       </c>
       <c r="M487" s="4" t="inlineStr">
@@ -31487,7 +31487,7 @@
       </c>
       <c r="C488" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D488" s="4" t="inlineStr">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +58.1pp alpha</t>
+          <t>Outperformance exit · +58.1 pp</t>
         </is>
       </c>
       <c r="M488" s="4" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D489" s="4" t="inlineStr">
@@ -31583,7 +31583,7 @@
       </c>
       <c r="L489" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +37.8pp alpha</t>
+          <t>Outperformance exit · +37.8 pp</t>
         </is>
       </c>
       <c r="M489" s="4" t="inlineStr">
@@ -31605,7 +31605,7 @@
       </c>
       <c r="C490" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D490" s="4" t="inlineStr">
@@ -31642,7 +31642,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +64.5pp alpha</t>
+          <t>Outperformance exit · +64.5 pp</t>
         </is>
       </c>
       <c r="M490" s="4" t="inlineStr">
@@ -31664,7 +31664,7 @@
       </c>
       <c r="C491" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D491" s="4" t="inlineStr">
@@ -31701,7 +31701,7 @@
       </c>
       <c r="L491" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +6.0pp alpha</t>
+          <t>Outperformance exit · +6.0 pp</t>
         </is>
       </c>
       <c r="M491" s="4" t="inlineStr">
@@ -31723,7 +31723,7 @@
       </c>
       <c r="C492" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D492" s="4" t="inlineStr">
@@ -31760,7 +31760,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +63.2pp alpha</t>
+          <t>Outperformance exit · +63.2 pp</t>
         </is>
       </c>
       <c r="M492" s="4" t="inlineStr">
@@ -31782,7 +31782,7 @@
       </c>
       <c r="C493" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D493" s="4" t="inlineStr">
@@ -31819,7 +31819,7 @@
       </c>
       <c r="L493" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +58.2pp alpha</t>
+          <t>Outperformance exit · +58.2 pp</t>
         </is>
       </c>
       <c r="M493" s="4" t="inlineStr">
@@ -31841,7 +31841,7 @@
       </c>
       <c r="C494" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D494" s="4" t="inlineStr">
@@ -31878,7 +31878,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +45.6pp alpha</t>
+          <t>Outperformance exit · +45.6 pp</t>
         </is>
       </c>
       <c r="M494" s="4" t="inlineStr">
@@ -31900,7 +31900,7 @@
       </c>
       <c r="C495" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D495" s="4" t="inlineStr">
@@ -31937,7 +31937,7 @@
       </c>
       <c r="L495" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +14.8pp alpha</t>
+          <t>Outperformance exit · +14.8 pp</t>
         </is>
       </c>
       <c r="M495" s="4" t="inlineStr">
@@ -31959,7 +31959,7 @@
       </c>
       <c r="C496" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D496" s="4" t="inlineStr">
@@ -31996,7 +31996,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +43.9pp alpha</t>
+          <t>Outperformance exit · +43.9 pp</t>
         </is>
       </c>
       <c r="M496" s="4" t="inlineStr">
@@ -32018,7 +32018,7 @@
       </c>
       <c r="C497" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D497" s="4" t="inlineStr">
@@ -32055,7 +32055,7 @@
       </c>
       <c r="L497" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +14.4pp alpha</t>
+          <t>Outperformance exit · +14.4 pp</t>
         </is>
       </c>
       <c r="M497" s="4" t="inlineStr">
@@ -32077,7 +32077,7 @@
       </c>
       <c r="C498" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D498" s="4" t="inlineStr">
@@ -32114,7 +32114,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +58.0pp alpha</t>
+          <t>Outperformance exit · +58.0 pp</t>
         </is>
       </c>
       <c r="M498" s="4" t="inlineStr">
@@ -32136,7 +32136,7 @@
       </c>
       <c r="C499" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D499" s="4" t="inlineStr">
@@ -32173,7 +32173,7 @@
       </c>
       <c r="L499" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +37.2pp alpha</t>
+          <t>Outperformance exit · +37.2 pp</t>
         </is>
       </c>
       <c r="M499" s="4" t="inlineStr">
@@ -32195,7 +32195,7 @@
       </c>
       <c r="C500" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D500" s="4" t="inlineStr">
@@ -32232,7 +32232,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +13.0pp alpha</t>
+          <t>Outperformance exit · +13.0 pp</t>
         </is>
       </c>
       <c r="M500" s="4" t="inlineStr">
@@ -32254,7 +32254,7 @@
       </c>
       <c r="C501" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D501" s="4" t="inlineStr">
@@ -32291,7 +32291,7 @@
       </c>
       <c r="L501" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +15.5pp alpha</t>
+          <t>Outperformance exit · +15.5 pp</t>
         </is>
       </c>
       <c r="M501" s="4" t="inlineStr">
@@ -32313,7 +32313,7 @@
       </c>
       <c r="C502" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D502" s="4" t="inlineStr">
@@ -32350,7 +32350,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +45.9pp alpha</t>
+          <t>Outperformance exit · +45.9 pp</t>
         </is>
       </c>
       <c r="M502" s="4" t="inlineStr">
@@ -32372,7 +32372,7 @@
       </c>
       <c r="C503" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D503" s="4" t="inlineStr">
@@ -32409,7 +32409,7 @@
       </c>
       <c r="L503" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +16.4pp alpha</t>
+          <t>Outperformance exit · +16.4 pp</t>
         </is>
       </c>
       <c r="M503" s="4" t="inlineStr">
@@ -32431,7 +32431,7 @@
       </c>
       <c r="C504" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D504" s="4" t="inlineStr">
@@ -32468,7 +32468,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +15.2pp alpha</t>
+          <t>Outperformance exit · +15.2 pp</t>
         </is>
       </c>
       <c r="M504" s="4" t="inlineStr">
@@ -32490,7 +32490,7 @@
       </c>
       <c r="C505" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D505" s="4" t="inlineStr">
@@ -32527,7 +32527,7 @@
       </c>
       <c r="L505" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +12.2pp alpha</t>
+          <t>Outperformance exit · +12.2 pp</t>
         </is>
       </c>
       <c r="M505" s="4" t="inlineStr">
@@ -32549,7 +32549,7 @@
       </c>
       <c r="C506" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D506" s="4" t="inlineStr">
@@ -32586,7 +32586,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +6.6pp alpha</t>
+          <t>Outperformance exit · +6.6 pp</t>
         </is>
       </c>
       <c r="M506" s="4" t="inlineStr">
